--- a/03_Group_comparisons/Proteome_clusters/c_data/01_design_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome_clusters/c_data/01_design_contrasts_all_inputs.xlsx
@@ -90,13 +90,13 @@
     <t>role</t>
   </si>
   <si>
-    <t>How the contrast is read: primary, secondary, descriptive, or floor (the baseline group difference).</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Feature level: proteins, sets or modules.</t>
+    <t>How the contrast is read: primary, secondary, descriptive, or baseline_reference (the baseline group difference).</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>What a correlation is estimated within.</t>
   </si>
   <si>
     <t>correlation</t>
@@ -183,7 +183,7 @@
     <t>Baseline_C1vC2</t>
   </si>
   <si>
-    <t>floor</t>
+    <t>baseline_reference</t>
   </si>
   <si>
     <t>Trained_C1vC2 = C1_T2 - C2_T2</t>
@@ -234,31 +234,31 @@
     <t>03_Group_comparisons/Proteome_T1/c_data/01_design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>2cc64ae6d564e288c2243bc302e1135e</t>
+    <t>ad32ff19ae61244c4bca6c11f0f8ab28</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T2/c_data/01_design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>2414a7a7483db00ed721b00271a44b77</t>
+    <t>b29bb85dd605c33d636e44acf2c5f3e0</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_T3/c_data/01_design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>57b5ec049b8fea1e8383d5f676850383</t>
+    <t>a71361a37853a674814f5336ba79e7c6</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_training/c_data/01_design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>828bdacdff6a362698dc15b4f8f11125</t>
+    <t>7dee957c9f00ca6124faae188e67d7bb</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome_acute/c_data/01_design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>2582548aeb4f7ace4217f73360a23067</t>
+    <t>ba6f56dbeec63a412d98c7cd8423cdc2</t>
   </si>
   <si>
     <t>BiocGenerics</t>
